--- a/rules/sources/openfigi/MAPPING.xlsx
+++ b/rules/sources/openfigi/MAPPING.xlsx
@@ -1035,7 +1035,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rules/sources/openfigi/MAPPING.xlsx
+++ b/rules/sources/openfigi/MAPPING.xlsx
@@ -638,15 +638,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -678,6 +678,62 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
         </is>
       </c>
     </row>
@@ -934,15 +990,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -974,6 +1030,70 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
         </is>
       </c>
     </row>

--- a/rules/sources/openfigi/MAPPING.xlsx
+++ b/rules/sources/openfigi/MAPPING.xlsx
@@ -638,13 +638,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
@@ -712,28 +712,252 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>security_type</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>market_sector</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>market_sector</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.market_sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.share_class_figi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>MDM field</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>market_sector</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>market_sector</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.market_sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.share_class_figi</t>
         </is>
       </c>
     </row>
@@ -990,11 +1214,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1041,12 +1265,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>market_sector</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1092,6 +1316,262 @@
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>market_sector</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/sources/openfigi/MAPPING.xlsx
+++ b/rules/sources/openfigi/MAPPING.xlsx
@@ -1302,7 +1302,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">

--- a/rules/sources/openfigi/MAPPING.xlsx
+++ b/rules/sources/openfigi/MAPPING.xlsx
@@ -638,13 +638,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
@@ -712,28 +712,252 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>security_type</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>market_sector</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>market_sector</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.market_sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.share_class_figi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>MDM field</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>market_sector</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>market_sector</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.market_sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.share_class_figi</t>
         </is>
       </c>
     </row>
@@ -990,11 +1214,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1041,12 +1265,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>market_sector</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1078,7 +1302,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1092,6 +1316,262 @@
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>market_sector</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/sources/openfigi/MAPPING.xlsx
+++ b/rules/sources/openfigi/MAPPING.xlsx
@@ -638,13 +638,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
@@ -796,18 +796,18 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>share_class_figi</t>
+          <t>name_of_issuer</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>share_class_figi</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.share_class_figi</t>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
         </is>
       </c>
     </row>
@@ -829,13 +829,13 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>security_type</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>security_type</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type</t>
         </is>
       </c>
     </row>
@@ -857,13 +857,13 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>security_type</t>
+          <t>security_type2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>security_type</t>
+          <t>security_type2</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type</t>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type2</t>
         </is>
       </c>
     </row>
@@ -885,13 +885,13 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>security_type2</t>
+          <t>market_sector</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>security_type2</t>
+          <t>market_sector</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -901,63 +901,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>market_sector</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>market_sector</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>MDM field</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
           <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.market_sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>share_class_figi</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>share_class_figi</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>MDM field</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.share_class_figi</t>
         </is>
       </c>
     </row>
@@ -1214,11 +1158,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1393,7 +1337,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>share_class_figi</t>
+          <t>market_sector</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1425,12 +1369,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>market_sector</t>
+          <t>name_of_issuer</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1457,12 +1401,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>security_type</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1489,7 +1433,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>security_type</t>
+          <t>security_type2</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1508,70 +1452,6 @@
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>security_type2</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>share_class_figi</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/sources/openfigi/MAPPING.xlsx
+++ b/rules/sources/openfigi/MAPPING.xlsx
@@ -916,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1036,6 +1036,43 @@
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>mdm.openfigi.security_isin.v1.contract.adapter.identifiers.isin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>cusip</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>figi_cusip</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>cusip</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Only with a new dataset code</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>mdm.openfigi.security_isin.v1.contract.adapter.identifiers.cusip</t>
         </is>
       </c>
     </row>

--- a/rules/sources/openfigi/MAPPING.xlsx
+++ b/rules/sources/openfigi/MAPPING.xlsx
@@ -558,7 +558,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1: provider</t>
+          <t>openfigi.security_isin.v2: provider</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -570,7 +570,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1: kind</t>
+          <t>openfigi.security_isin.v2: kind</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1: one record is</t>
+          <t>openfigi.security_isin.v2: one record is</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1: one publication is</t>
+          <t>openfigi.security_isin.v2: one publication is</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1: a file covers</t>
+          <t>openfigi.security_isin.v2: a file covers</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1: set aside without stopping the run</t>
+          <t>openfigi.security_isin.v2: set aside without stopping the run</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1</t>
+          <t>openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -817,14 +817,14 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
+          <t>mdm.openfigi.security_isin.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1</t>
+          <t>openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -845,14 +845,14 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type</t>
+          <t>mdm.openfigi.security_isin.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1</t>
+          <t>openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -873,14 +873,14 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type2</t>
+          <t>mdm.openfigi.security_isin.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1</t>
+          <t>openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.market_sector</t>
+          <t>mdm.openfigi.security_isin.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.market_sector</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1</t>
+          <t>openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1035,14 +1035,14 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security_isin.v1.contract.adapter.identifiers.isin</t>
+          <t>mdm.openfigi.security_isin.v2.contract.adapter.identifiers.isin</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1</t>
+          <t>openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security_isin.v1.contract.adapter.identifiers.cusip</t>
+          <t>mdm.openfigi.security_isin.v2.contract.adapter.identifiers.cusip</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">

--- a/rules/sources/openfigi/MAPPING.xlsx
+++ b/rules/sources/openfigi/MAPPING.xlsx
@@ -428,10 +428,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -486,7 +486,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1: provider</t>
+          <t>openfigi.security.v3: provider</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -498,7 +498,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1: kind</t>
+          <t>openfigi.security.v3: kind</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -510,19 +510,19 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1: one record is</t>
+          <t>openfigi.security.v3: one record is</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>the CUSIP asked, upper-cased; one record per CUSIP asked</t>
+          <t>the CUSIP or ISIN asked, upper-cased; one record per identifier asked</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1: one publication is</t>
+          <t>openfigi.security.v3: one publication is</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -534,96 +534,24 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1: a file covers</t>
+          <t>openfigi.security.v3: a file covers</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>the CUSIPs asked of OpenFIGI; no retirement by absence</t>
+          <t>the CUSIPs and ISINs asked of OpenFIGI; no retirement by absence</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1: set aside without stopping the run</t>
+          <t>openfigi.security.v3: set aside without stopping the run</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>invalid_cusip, invalid_cusip_checksum, missing_record_identity, not_found_by_openfigi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v2: provider</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>OpenFIGI</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v2: kind</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v2: one record is</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>the ISIN asked, upper-cased; one record per ISIN asked</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v2: one publication is</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>the capture's mapping answer files and the reduce, combine and record contracts</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v2: a file covers</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>the ISINs asked of OpenFIGI; no retirement by absence</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v2: set aside without stopping the run</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>invalid_isin, invalid_isin_checksum, missing_record_identity, not_found_by_openfigi</t>
+          <t>invalid_cusip, invalid_cusip_checksum, invalid_isin, invalid_isin_checksum, invalid_figi, invalid_figi_checksum, missing_record_identity, not_found_by_openfigi</t>
         </is>
       </c>
     </row>
@@ -638,10 +566,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -684,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -705,14 +633,14 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
+          <t>mdm.openfigi.security.v3.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -733,14 +661,14 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type</t>
+          <t>mdm.openfigi.security.v3.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -761,14 +689,14 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type2</t>
+          <t>mdm.openfigi.security.v3.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,119 +717,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.market_sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v2</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>name_of_issuer</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>MDM field</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>mdm.openfigi.security_isin.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v2</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>security_type</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>security_type</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>MDM field</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>mdm.openfigi.security_isin.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v2</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>security_type2</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>security_type2</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>MDM field</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>mdm.openfigi.security_isin.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.security_type2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v2</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>market_sector</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>market_sector</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>MDM field</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>mdm.openfigi.security_isin.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.market_sector</t>
+          <t>mdm.openfigi.security.v3.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.market_sector</t>
         </is>
       </c>
     </row>
@@ -919,13 +735,13 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
+    <col width="61" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -968,7 +784,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -978,7 +794,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>cusip</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -998,14 +814,14 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security.v1.contract.adapter.identifiers.cusip</t>
+          <t>mdm.openfigi.security.v3.contract.adapter.identifiers.cusip</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v2</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1015,7 +831,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>isin</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1035,29 +851,29 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security_isin.v2.contract.adapter.identifiers.isin</t>
+          <t>mdm.openfigi.security.v3.contract.adapter.identifiers.isin</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v2</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>cusip</t>
+          <t>figi</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>figi_cusip</t>
+          <t>figis</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>cusip</t>
+          <t>figi</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1072,7 +888,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>mdm.openfigi.security_isin.v2.contract.adapter.identifiers.cusip</t>
+          <t>mdm.openfigi.security.v3.contract.adapter.identifiers.figi</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1251,12 +1067,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1283,12 +1099,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v3, sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1315,12 +1131,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1347,12 +1163,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1361,134 +1177,6 @@
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>market_sector</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>name_of_issuer</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>security_type</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>security_type2</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/sources/openfigi/MAPPING.xlsx
+++ b/rules/sources/openfigi/MAPPING.xlsx
@@ -13,7 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critical data elements" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data quality" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Who wins" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline targets" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline steps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1193,6 +1195,597 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Run checks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lease seconds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Heartbeat seconds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>manifest.hash, work.accounting, journal.delivered</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Requires</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>answers</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>source.combine</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>answers</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.combined</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>line_counts</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>source.combine</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>answers</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.combined</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>lines</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>source.combine</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>line_counts, answers</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.combined</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>listing</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>lines</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>combine</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>source.combine</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>reduce, answers, listing</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.combined</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>combine</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[7]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>mdm.prepare</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, mdm.prepared</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[8]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>mdm.merge</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>{batch_id}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>mdm:consumer:{consumer}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, mdm.committed</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[9]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>processed</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>journal.record</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, journal.recorded</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[10]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
